--- a/Empréstimos.xlsx
+++ b/Empréstimos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/368431DEF48B862B/Banco Gênio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="879" documentId="8_{95C22E98-A0ED-4406-BE39-0895A6A0D707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41379ADB-F14C-41EF-AF39-BFD894B54FBD}"/>
+  <xr:revisionPtr revIDLastSave="886" documentId="8_{95C22E98-A0ED-4406-BE39-0895A6A0D707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4043C614-204B-4587-8A60-D54F78B27BD1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{FD4637E9-BD7F-4D4F-BAA8-763A943EC97F}"/>
   </bookViews>
@@ -478,7 +478,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -563,9 +563,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3567,14 +3564,16 @@
       <c r="G25" s="15">
         <v>46077</v>
       </c>
-      <c r="H25" s="15"/>
+      <c r="H25" s="15">
+        <v>46079</v>
+      </c>
       <c r="I25" s="18">
         <f ca="1">Tabela2[[#This Row],[Vencimento]]-TODAY()</f>
-        <v>16</v>
-      </c>
-      <c r="J25" s="18" t="str">
+        <v>-11</v>
+      </c>
+      <c r="J25" s="18">
         <f ca="1">IF(TODAY()-G25&lt;0,"No prazo",IF(Tabela2[[#This Row],[Status]]="Pago",Tabela2[[#This Row],[Dia pagamento]]-Tabela2[[#This Row],[Vencimento]],TODAY()-G25))</f>
-        <v>No prazo</v>
+        <v>2</v>
       </c>
       <c r="K25" s="13">
         <v>1</v>
@@ -3584,22 +3583,22 @@
       </c>
       <c r="M25" s="14" cm="1">
         <f t="array" aca="1" ref="M25" ca="1">(C25+(C25*(E25*Tabela2[[#This Row],[Parcelas]]))+(C25*(Tabela1[I.O.F Diário]*Clientes!I25)))/K25+IF(TODAY()&gt;G25,(C25*(F25*J25)),0)</f>
-        <v>103.38120000000001</v>
+        <v>105.1598</v>
       </c>
       <c r="N25" s="19">
         <f ca="1">M25*K25</f>
-        <v>103.38120000000001</v>
+        <v>105.1598</v>
       </c>
       <c r="O25" s="19" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="P25" s="19">
         <f ca="1">Tabela2[[#This Row],[Total]]-Tabela2[[#This Row],[Valor]]</f>
-        <v>3.3812000000000069</v>
+        <v>5.1598000000000042</v>
       </c>
       <c r="Q25" s="32">
         <f ca="1">Tabela2[[#This Row],[Valor parcela]]*Tabela2[[#This Row],[Parcelas faltantes]]</f>
-        <v>103.38120000000001</v>
+        <v>105.1598</v>
       </c>
       <c r="R25" s="36">
         <f ca="1">Q22</f>
@@ -3772,9 +3771,9 @@
         <v>24</v>
       </c>
       <c r="L28" s="13">
-        <v>24</v>
-      </c>
-      <c r="M28" s="40" cm="1">
+        <v>23</v>
+      </c>
+      <c r="M28" s="14" cm="1">
         <f t="array" aca="1" ref="M28" ca="1">(C28+(C28*(E28*Tabela2[[#This Row],[Parcelas]]))+(C28*(Tabela1[I.O.F Diário]*Clientes!I28)))/K28+IF(TODAY()&gt;G28,(C28*(F28*J28)),0)</f>
         <v>905.72876363996284</v>
       </c>
@@ -3791,7 +3790,7 @@
       </c>
       <c r="Q28" s="35">
         <f ca="1">Tabela2[[#This Row],[Valor parcela]]*Tabela2[[#This Row],[Parcelas faltantes]]</f>
-        <v>21737.490327359108</v>
+        <v>20831.761563719145</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3799,8 +3798,8 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="Q32" s="36">
-        <f ca="1">Q25+Q28</f>
-        <v>21840.871527359108</v>
+        <f ca="1">Q28</f>
+        <v>20831.761563719145</v>
       </c>
     </row>
   </sheetData>
@@ -4046,7 +4045,7 @@
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <f ca="1">SUMIF(Tabela2[Status],"À Pagar",Tabela2[Valor Faltante])</f>
-        <v>21840.871527359108</v>
+        <v>20831.761563719145</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
